--- a/Portfolio main.xlsx
+++ b/Portfolio main.xlsx
@@ -27,10 +27,16 @@
     <t>Age</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
     <t>img1 address</t>
   </si>
   <si>
-    <t>Category</t>
+    <t>Img1 address</t>
   </si>
   <si>
     <t>img1 caption</t>
@@ -39,163 +45,145 @@
     <t>Creation Date Rank (1 = Newest)</t>
   </si>
   <si>
-    <t>Order</t>
-  </si>
-  <si>
     <t>Education</t>
   </si>
   <si>
+    <t>Date Code</t>
+  </si>
+  <si>
     <t>W_GPA</t>
   </si>
   <si>
-    <t>Date Code</t>
-  </si>
-  <si>
-    <t>Img1 address</t>
+    <t>Pride Rank (1 = Highest)</t>
   </si>
   <si>
     <t>UW_GPA</t>
   </si>
   <si>
-    <t>Pride Rank (1 = Highest)</t>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>Domain</t>
   </si>
   <si>
     <t>Focus</t>
   </si>
   <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Linkedin</t>
+  </si>
+  <si>
+    <t>Subtitle</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Disciplines</t>
+  </si>
+  <si>
+    <t>Main Text</t>
+  </si>
+  <si>
+    <t>Noah Walsh</t>
+  </si>
+  <si>
+    <t>Vid or photo address 1</t>
+  </si>
+  <si>
     <t>Img1 caption</t>
   </si>
   <si>
-    <t>Github</t>
-  </si>
-  <si>
-    <t>Linkedin</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>Domain</t>
+    <t>Vid or photo caption 1</t>
+  </si>
+  <si>
+    <t>images/me.png</t>
+  </si>
+  <si>
+    <t>Vid or photo address 2</t>
+  </si>
+  <si>
+    <t>Photo taken at ARC National Competition 2025-2026</t>
   </si>
   <si>
     <t>Role</t>
   </si>
   <si>
-    <t>Noah Walsh</t>
-  </si>
-  <si>
-    <t>Subtitle</t>
-  </si>
-  <si>
-    <t>images/me.png</t>
+    <t>Vid or photo caption 2</t>
+  </si>
+  <si>
+    <t>Senior at Scripps Ranch High School</t>
+  </si>
+  <si>
+    <t>Vid or photo address 3</t>
+  </si>
+  <si>
+    <t>Vid or photo caption 3</t>
+  </si>
+  <si>
+    <t>Mechanical &amp; Mechatronics Engineering</t>
   </si>
   <si>
     <t>SEAP</t>
   </si>
   <si>
-    <t>Photo taken at ARC National Competition 2025-2026</t>
-  </si>
-  <si>
-    <t>Disciplines</t>
-  </si>
-  <si>
-    <t>Senior at Scripps Ranch High School</t>
+    <t>Vid or photo address 4</t>
   </si>
   <si>
     <t>Internship</t>
   </si>
   <si>
-    <t>Main Text</t>
-  </si>
-  <si>
-    <t>Vid or photo address 1</t>
-  </si>
-  <si>
-    <t>Mechanical &amp; Mechatronics Engineering</t>
-  </si>
-  <si>
-    <t>Vid or photo caption 1</t>
+    <t>https://www.linkedin.com/in/noah-walsh-9766593a2/</t>
+  </si>
+  <si>
+    <t>Vid or photo caption 4</t>
+  </si>
+  <si>
+    <t>Outpost</t>
   </si>
   <si>
     <t>images/SEAP.png</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/noah-walsh-9766593a2/</t>
-  </si>
-  <si>
-    <t>Vid or photo address 2</t>
-  </si>
-  <si>
-    <t>Vid or photo caption 2</t>
-  </si>
-  <si>
     <t>Intern at Science &amp; Engineering Apprenticeship Program 2025</t>
   </si>
   <si>
-    <t>Vid or photo address 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">Completed an 8-week full-time engineering internship with full-time employment 8-to-5, 40 hours per week. I developed punctuality, communication, teamwork, and workplace professionalism, while collaborating with engineers and researchers on technical projects. I wrote data-analysis scripts to streamline scientific processes and ideated future solutions to loborius tasks. </t>
   </si>
   <si>
-    <t>Vid or photo caption 3</t>
-  </si>
-  <si>
-    <t>Vid or photo address 4</t>
-  </si>
-  <si>
     <t>ARC</t>
   </si>
   <si>
-    <t>Vid or photo caption 4</t>
-  </si>
-  <si>
     <t>Competetive Robotics</t>
   </si>
   <si>
+    <t xml:space="preserve">Github URL: https://github.com/loganw023/Sticks-Up/tree/main </t>
+  </si>
+  <si>
     <t>images/ARC.png</t>
   </si>
   <si>
-    <t>Outpost</t>
+    <t>ROBOTICS &amp; MACHINE LEARNING</t>
+  </si>
+  <si>
+    <t>Hack Club's Outpost, 48-hour hackathon Followed by Open Sauce, Attendee; 
+Stick's Up, a 2D fencing game project</t>
+  </si>
+  <si>
+    <t>Stick's Up — A 2D Robot Fencing Game</t>
   </si>
   <si>
     <t>Aerospace Robotics Competition Team Captain, Lead Mechanism Designer, Pilot and now Coach</t>
+  </si>
+  <si>
+    <t>Robotics, Mechanical, Electrical, and ML and Software Engineering</t>
   </si>
   <si>
     <t>Led engineering projects and competition operations
 Helped team achieve 1st place regionally and 3rd place nationally
 Adapted to major technical failures during competition</t>
-  </si>
-  <si>
-    <t>HC</t>
-  </si>
-  <si>
-    <t>Club Officer</t>
-  </si>
-  <si>
-    <t>images/HC.png</t>
-  </si>
-  <si>
-    <t>Will work on this soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Github URL: https://github.com/loganw023/Sticks-Up/tree/main </t>
-  </si>
-  <si>
-    <t>ROBOTICS &amp; MACHINE LEARNING</t>
-  </si>
-  <si>
-    <t>Hack Club's Outpost, 48-hour hackathon Followed by Open Sauce, Attendee; 
-Stick's Up, a 2D fencing game project</t>
-  </si>
-  <si>
-    <t>Stick's Up — A 2D Robot Fencing Game</t>
-  </si>
-  <si>
-    <t>Robotics, Mechanical, Electrical, and ML and Software Engineering</t>
   </si>
   <si>
     <t>Project summary: I was the main CADder and worked significantly on the electricals, especially when it needed repairs. After given the task to create a interactable project in 48 hours, Logan Wheatcroft, Mateo Johnson, and I decided to build a 2-dimensional robot fencing game. The project was finished in the 48hours, but the ML was not deployed in that time frame.
@@ -204,7 +192,19 @@
 Results and impact: The project was presented at OpenSauce and many Hack Clubbers and some fans played the game.</t>
   </si>
   <si>
+    <t>HC</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=ImYCyPfYhdE</t>
+  </si>
+  <si>
+    <t>Club Officer</t>
+  </si>
+  <si>
+    <t>Will work on this soon</t>
+  </si>
+  <si>
+    <t>images/HC.png</t>
   </si>
   <si>
     <t>Testing controls and degrees of freedom</t>
@@ -237,13 +237,13 @@
 Results and impact: In our first year, the team placed 4th at the San Diego Regional competition, 50 points (5000 total) from 3rd and an invitation to the National Competition; we also earned the Sportsmanship award. In its second year, the team placed 1st at the San Diego Regional, securing the most points at any regional) and Third at the National Competition, despite having a budget roughly 55% of most other teams. We also learned that despite the worst beginnings, comebacks are usually possible; both the beginning of the first Regional Competition and the National Competition were complete disasters).</t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQWpO8XGNiNv9VSdlI2uLFSmj2KNq6Ze7KMWu67B2-539ilEZkOYMkY4IXYyWVbjUKeVIYg6Noo6Vuk6uRZ7eobwLmaApfagK-f-BoSEUNVHS4m6F-5MxpvrpKVSZJM-1Z4xNxvjLuMwNJmgHmkNeHqqrGD8MiP5DiYeymC_hJUIi4QdbjKLSy6sxwJyt1g3mg2bPgwygDnJ7DPcsVimi_UhfjW92ve7PnOvyb_M=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQXR8avbML8DZQWMjOpjtpT5BCYGTXRQiZ3ncq3LMr9ybNUgYdoAliSemn9FS2ywmuweu15B5LPrr7BGmserBl--zJEWV6bJz_5ZbZo8urrFON9m-LEXxaSGt-KpBrE1ZYKlx9S-odjNpKEtLHxhXpleHLJ67aMXd1y2zQ9YWU602SN3oa-64exfxbbHILqIEyCQ1RM1Dxzvrv_zEVVKLM_EW3BSc-r1ktL6v8fBDzI=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQWT4VZChJSOjduyzd2QDSlkLwufLc-85QbAvlFTz5dUJPiSVQ72-ZxZQo93zj3UbP5K8lr2I8wi-EuiAPopc3-mOHABx-vsexiIxZhuO_GEYT4R9Mm89zYT6oL3-QxJKAYiqqbtMrXg5vdqlu_V2-8GgakNi_S6fg03qne_hDLUTVgJsnSPJhQlG29tCdN3cu8rFlH-Edu9rojTh3pbimpRFY0zL0kRD00p9VlLZmI=w1280</t>
+    <t>images/ARC 1.jpg</t>
+  </si>
+  <si>
+    <t>images/ARC 2.png</t>
+  </si>
+  <si>
+    <t>images/ARC 3.png</t>
   </si>
   <si>
     <t>Proto</t>
@@ -270,7 +270,7 @@
 Results and impact: Though we did not place (we were likely nowhere close), I learned significantly about training AI models. You must teach them like you are teaching chess: you must show the basics, then you can build up; work with the simple things first; take steps.</t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQVCWM4alHbPwIEZEEls0-K-Ce05bWHyt9Oeanudna3rtTpNAYWqAheQ5k25riArc1Ue8dank0NYJcLXLmbR3Vm7Ab0oRYXAM0e64pRmgyyKfkC66t9T8UQ3zFbNVSFg5UiZmS2HNt-T_h79gWc5DlawMPFszk9RU-7WrkHMxXiUIt13wJCaDF-NWqdFAbCxwi1yZq8zZXD93Jh1TvTaLrBQuHIzgoim19EGIp_8aFE=w1280</t>
+    <t>images/Arm 1.png</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=po0gLzeUUdQ</t>
@@ -300,16 +300,16 @@
 Results and impact: I created a PCB project, learned how to use KiCad, and how to debug using Thonny.</t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQUnauv51lAHtY6_04pF-xKHVSoJxXEnevCKSPkGyo91ERBaQhw5izWrMdGanOBcVb3-K0kE1dQA3Ht-qehRzlBUJPyhs5KjZmLrtYVdHIIx6tFZQEjx-i6QI2CY11bQ_slzUrMIqxw6tLQu_f1XhrlH45DNV56PhCZfcItf_gtgQtK9av8-ackeqe23m5UILladXBKPZJaMTxXmpw-ZbWCc3aYtao36zNZiL5edzPE=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQXJhiQaT-szzFdSM0tNf4wRwngt6l2xeh5ngAOidMYa2UcC68gBzcH8zH7cbPkc5J7WP4ReU-K7hzBfKAVaVYnAfFtkY4_liZVqGf-NHozJN8lOJxahsZIWgFcG2admKsP70qbl5R6Z3KxMjaVeP21ogVdxxa-lGvJtuy3oJrg0fhJjPZd4JQwzruruBvSip7lGMakxG_bEViTG_ssAGz5XUxk0ChXHjnX90GYaQA8=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQV3W5cpYBOnNB2Hq1gBAnhl-zNp8_bG2cuYCfxBudyMTO2wxVAay35vlUffMkPDiyceS_6jyhROZ7-ACR-36k1NBGuvzugGBF0UfvFLo3cAdRkxTORLFk0t83hzY4d3J2NZdo8eve4aUZiwC5OoGEozSk7l1wMQL5dCjV7x127MqpcyH3PPKKLpMwfHV-FYbCg768XMlanjTr7ih-XyhbxetWvAnYXUFsJewuHs=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQW7kx3ct1pFiW1Wk739U7mKMldB81nceCESZEKyg8VTXWrEW0zusxxNOeCEpdl0kjHomDg7lp7TBVbzJTDFd9PgOXan1hriJGgCffyhpcH2Dv5y1zyzrq_Yj6IoaqYlgu9nZJPOZZf5ctu21nidriM1aj4HaH-P18_7Yf7IAznNCnZFd9k8lTfs8xIPVgQVb68PO2hTZ2skyBmgL7ZZWE4GouJosr1NrDG1o_ip=w1280</t>
+    <t>images/Keeb 1.png</t>
+  </si>
+  <si>
+    <t>images/Keeb 2.jpg</t>
+  </si>
+  <si>
+    <t>images/Keeb 3.png</t>
+  </si>
+  <si>
+    <t>images/Keeb 4.png</t>
   </si>
   <si>
     <t>Wind</t>
@@ -342,10 +342,10 @@
     <t xml:space="preserve">This is the only video I got before lending the mister out at OpenSauce; I did not get it back. </t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQV_PDBaR8MynYZs6xQmUL7jkCVJgkiYD9YI2OsMH95DYB_5tPCSzgCheq_GJqATiLIiBwKHZYDA2nUJd_5nTlNeqrul93N19WuT1fCIWt5WrmUBgBbGwwwVczpvaWj-wThI1_fmIjYwtt9P2GibHLkQVFhW2ajcfVnWOrRnqN4oRROUmXCmyij8xeekSge0FJedfimuNOHIXuUwmoG6sKgfRxQFq07y-tiCUyPElis=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQVnm8dFYfpedhwJs-nraQRsqwlgoLGfUgT4BdZnHd7cZcPhudcV9zK9YonKwpGZ08bLuhReQNnWsIQ1p7MFRngm9jXbuoMmUHRuZU2sy0GQWtrS_ZupHf0Z4_5dF6QNlVNgJvGDJIsMf1EAkQqv_7UdFM0anV1y5jyGyviUI4Y5V3CadLSQ1xl1lrQXgEH2fT9CYaOVVQksyegOIQB4_y4_UFkC5iuclixyfJJL=w1280</t>
+    <t>images/Air 1.jpg</t>
+  </si>
+  <si>
+    <t>images/Air 2.png</t>
   </si>
   <si>
     <t>Balancer</t>
@@ -372,10 +372,10 @@
 Results and impact: I learned basic PID controls and built a balancing platform.</t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQXFlxU0jC_q_SWjuezG2qbP-tP5gSuD9gzKGy806Tcqfmqa5N3oqaqF7_YNBkyXY-Ycz9SSGpWfgs9teQTdzw1PKS-r0Rljr6JQEZlvjz9FEjyhEB2Ve5dnh6bgofYn-Zr7pU38Q4RHrKabXlnClBqGChqlUjyhu0jNdwgPkvQFVX5cRGKOm9Z4mGPNL2bvcgo3ZJBAm3FEy0CiANh-_bzB1Yei-wo3h1JOfnDJ=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQWmREecphV55gyp3VCE8JVJje_nvxtGFDUO_HSeBbR1P5MsS3dCyYUrMabHy_lCcVMQEe3rdsFiKDcuEJITILCoHPG9Zpv0x1Iszr1V6LaST19Ph9bj6juOnEFS6topBv8OTSzizDG46_4niSJTx7eiYSwLG4yh6SMCHBDFqYTKwDGXWuHFElJ-mb-_hxp092zmunInsXI0nK0vv1eN9gI-w_TDVqVXRRPeSD4n7mY=w1280</t>
+    <t>images/Balance 2.png</t>
+  </si>
+  <si>
+    <t>images/Balance 1.png</t>
   </si>
   <si>
     <t>Flying Wing</t>
@@ -402,10 +402,10 @@
 Results and impact: I learned significantly about air foils and the importance of balancing weight in a fixed-wing drone.</t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQW1218EwCso_c81Ojaw8u6KAN3iXxReYvoUK8atgHSRnlcMxIriwK1OcW2hfOhzaaXc8Vg1F50PTMSn0rQQiaNsveavgUccdld4YuZHIRKkUSs-JPCBDrgleDX3PKcCIC47NVFtFYGoKkRjrcQNN9Xtc8E9hB3imtAXxdU0LsjEOsXZSnoGoLbdcTFskpEtuZ18UVr06TYs2ukl-1BAmiZJv2zqNL7zma4EEAfL=w1280</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQU-iJbiwiIv3fjLP2KnM7lFBOYGZOOeLkKtmWfyBqEX7lxpX3wRMAqi6ACpLA-ZMouNuvZ_Ulttq6DaaV2-0tB2nH8u04PlYV79b_tKkQLK4FvUHawJm4MP6rvXvG6QifZZC9hXkcHnW8yTQ0tQtX4PCyes1PTwupq8oZpAI_6w2Qfrn-wLZfCQ1me6Hl5e4TIjcvWHwGv8bKK558Ti4BNU6wv4-2vyclEtRYl1MOY=w1280</t>
+    <t>images/Flight 1.png</t>
+  </si>
+  <si>
+    <t>images/Flight 2.png</t>
   </si>
   <si>
     <t>Rover</t>
@@ -432,7 +432,7 @@
 Results and impact: We placed 14th at the San DIego regionals, 2 places from medaling. This was surprising after the encoders completely fried, leaving us with nothing on the day of the competition.</t>
   </si>
   <si>
-    <t>https://lh3.googleusercontent.com/sitesv/AG8ngQWfE-nQ4LZ6pgfsM1a5kF9C_IhADw-dlGy_4hswDh-vsaic0xyGivoJ1x4QEahJCSmLxh55EcAA7ZvbJ4zwLgGHaQ_rM6oGxILm0wN7VBHLKSIyjQrDv5zUvq1meCPPQZTlZQwjzpppFg1MzzmlwAINhCxXfIW46lT_ya5NBaXcEaIHBXlzay9UtOlXO59rjP9qUIqKCItCV2nEGL1LkiDMmhMyr31qXLG3aEls=w1280</t>
+    <t>images/Car 1.png</t>
   </si>
 </sst>
 </file>
@@ -719,60 +719,60 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -784,25 +784,25 @@
         <v>2.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>62</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1">
         <v>5.0</v>
@@ -845,13 +845,13 @@
       <c r="J3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -886,7 +886,7 @@
       <c r="J4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="1" t="s">
         <v>81</v>
       </c>
       <c r="M4" s="3" t="s">
@@ -924,16 +924,16 @@
       <c r="J5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="1" t="s">
         <v>93</v>
       </c>
     </row>
@@ -974,10 +974,10 @@
       <c r="L6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1012,10 +1012,10 @@
       <c r="J7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="K7" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="M7" s="1" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1048,10 +1048,10 @@
       <c r="J8" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="1" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1086,32 +1086,17 @@
       <c r="J9" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="1" t="s">
         <v>130</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="K2"/>
-    <hyperlink r:id="rId2" ref="K3"/>
-    <hyperlink r:id="rId3" ref="M3"/>
-    <hyperlink r:id="rId4" ref="O3"/>
-    <hyperlink r:id="rId5" ref="K4"/>
-    <hyperlink r:id="rId6" ref="M4"/>
-    <hyperlink r:id="rId7" ref="K5"/>
-    <hyperlink r:id="rId8" ref="M5"/>
-    <hyperlink r:id="rId9" ref="O5"/>
-    <hyperlink r:id="rId10" ref="Q5"/>
-    <hyperlink r:id="rId11" ref="K6"/>
-    <hyperlink r:id="rId12" ref="M6"/>
-    <hyperlink r:id="rId13" ref="O6"/>
-    <hyperlink r:id="rId14" ref="M7"/>
-    <hyperlink r:id="rId15" ref="O7"/>
-    <hyperlink r:id="rId16" ref="K8"/>
-    <hyperlink r:id="rId17" ref="M8"/>
-    <hyperlink r:id="rId18" ref="K9"/>
+    <hyperlink r:id="rId2" ref="M4"/>
+    <hyperlink r:id="rId3" ref="K6"/>
   </hyperlinks>
-  <drawing r:id="rId19"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -1127,91 +1112,91 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1">
         <v>3.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1234,45 +1219,45 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1">
         <v>17.0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1">
         <v>4.48</v>
@@ -1281,13 +1266,13 @@
         <v>3.95</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
